--- a/Zestawienie_Finansowe.xlsx
+++ b/Zestawienie_Finansowe.xlsx
@@ -8,19 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="Podsumowanie" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historia roczna" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Podsumowanie'!$1:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00 &quot;zł&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;zł&quot;;[Red]-#,##0.00 &quot;zł&quot;"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;zł&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00 &quot;zł&quot;;[Red](#,##0.00) &quot;zł&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,7 +37,18 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -48,31 +64,55 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00000000"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000070C0"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="11"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00375623"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="00375623"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="12"/>
+      <color rgb="00C00000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -86,8 +126,60 @@
       <color rgb="00595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000070C0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00BF9000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00BF9000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00BF9000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -96,7 +188,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,22 +208,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -134,8 +236,18 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF9000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -144,10 +256,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="00000000"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="00000000"/>
       </right>
       <top style="medium">
@@ -171,98 +283,191 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="20" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="24" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00375623"/>
+        <sz val="14"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00C00000"/>
+        <sz val="14"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -624,257 +829,1009 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>📊  ZESTAWIENIE FINANSOWE  —  PRZYCHODY &amp; WYDATKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Miesiąc / Rok:</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Sporządził: ________________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>PRZYCHODY  —  opis</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Kwota (PLN)</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Udział %</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>WYDATKI  —  opis</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Kwota (PLN)</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Udział %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="10" t="inlineStr"/>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Nazwa / kategoria</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Wartość w zł</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>% całości</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Nazwa / kategoria</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Wartość w zł</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>% całości</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>01.</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Sprzedaż produktów</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15">
+        <f>IF(C22=0,0,C6/C22)</f>
+        <v/>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Wynagrodzenia i ZUS</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="17">
+        <f>IF(F22=0,0,F6/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>02.</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Świadczenie usług</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15">
+        <f>IF(C22=0,0,C7/C22)</f>
+        <v/>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Czynsz i media</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17">
+        <f>IF(F22=0,0,F7/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>03.</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Wynajem nieruchomości</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
+        <f>IF(C22=0,0,C8/C22)</f>
+        <v/>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Materiały / surowce</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="17">
+        <f>IF(F22=0,0,F8/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>04.</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Przychody finansowe</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15">
+        <f>IF(C22=0,0,C9/C22)</f>
+        <v/>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Usługi zewnętrzne</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17">
+        <f>IF(F22=0,0,F9/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>05.</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Dotacje / dofinansowania</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15">
+        <f>IF(C22=0,0,C10/C22)</f>
+        <v/>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Marketing i reklama</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17">
+        <f>IF(F22=0,0,F10/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>06.</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Sprzedaż majątku</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
+        <f>IF(C22=0,0,C11/C22)</f>
+        <v/>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Paliwo i transport</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="17">
+        <f>IF(F22=0,0,F11/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>07.</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Prowizje i bonusy</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15">
+        <f>IF(C22=0,0,C12/C22)</f>
+        <v/>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Sprzęt / wyposażenie</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="17">
+        <f>IF(F22=0,0,F12/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>08.</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Refundacje i zwroty</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15">
+        <f>IF(C22=0,0,C13/C22)</f>
+        <v/>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Ubezpieczenia</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <f>IF(F22=0,0,F13/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>09.</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Licencje / tantiemy</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15">
+        <f>IF(C22=0,0,C14/C22)</f>
+        <v/>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Podatki i opłaty</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="17">
+        <f>IF(F22=0,0,F14/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>10.</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Działalność dodatkowa</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15">
+        <f>IF(C22=0,0,C15/C22)</f>
+        <v/>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Szkolenia i rozwój</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="17">
+        <f>IF(F22=0,0,F15/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>11.</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Przychód wyjątkowy</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15">
+        <f>IF(C22=0,0,C16/C22)</f>
+        <v/>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>Oprogramowanie / IT</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17">
+        <f>IF(F22=0,0,F16/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>12.</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Zaliczki na poczet usług</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15">
+        <f>IF(C22=0,0,C17/C22)</f>
+        <v/>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Koszty finansowe (odsetki)</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="17">
+        <f>IF(F22=0,0,F17/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>13.</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Sprzedaż online</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15">
+        <f>IF(C22=0,0,C18/C22)</f>
+        <v/>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Naprawy i utrzymanie</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="17">
+        <f>IF(F22=0,0,F18/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>14.</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Subskrypcje</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15">
+        <f>IF(C22=0,0,C19/C22)</f>
+        <v/>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Artykuły biurowe</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="17">
+        <f>IF(F22=0,0,F19/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>15.</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Inne przychody</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15">
+        <f>IF(C22=0,0,C20/C22)</f>
+        <v/>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>Inne wydatki</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="17">
+        <f>IF(F22=0,0,F20/ABS(F22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="6" customHeight="1">
+      <c r="A21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="20" t="inlineStr"/>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>✅  SUMA PRZYCHODÓW</t>
+        </is>
+      </c>
+      <c r="C22" s="22">
+        <f>SUM(C6:C20)</f>
+        <v/>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>❌  SUMA WYDATKÓW</t>
+        </is>
+      </c>
+      <c r="F22" s="25">
+        <f>-SUM(F6:F20)</f>
+        <v/>
+      </c>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>💰  WYNIK NETTO</t>
+        </is>
+      </c>
+      <c r="C24" s="28">
+        <f>C22+F22</f>
+        <v/>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Marża (%)</t>
+        </is>
+      </c>
+      <c r="F24" s="29">
+        <f>IF(C22=0,0,C24/C22)</f>
+        <v/>
+      </c>
+      <c r="G24" s="30" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>Liczba aktywnych pozycji — przychody:</t>
+        </is>
+      </c>
+      <c r="C25" s="32">
+        <f>COUNTIF(C6:C20,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Liczba aktywnych pozycji — wydatki:</t>
+        </is>
+      </c>
+      <c r="F25" s="34">
+        <f>COUNTIF(F6:F20,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1"/>
+    <row r="27" ht="8" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>🔵 Komórki NIEBIESKIE = wprowadź kwotę (PLN)   |   🟡 Żółte tło = pola do uzupełnienia   |   🟢 C22 = suma przychodów   |   🔴 F22 = suma wydatków (ujemna)   |   D2 = data okresu</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="G24"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A28:G28"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C24">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>📊  ZESTAWIENIE FINANSOWE — PRZYCHODY I WYDATKI</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Okres: ________________________   |   Sporządził: ________________________</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Nr</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>PRZYCHODY — kategoria</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Kwota (PLN)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>WYDATKI — kategoria</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Kwota (PLN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Sprzedaż towarów</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Wynagrodzenia i ZUS</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Świadczenie usług</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Czynsz i media</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Wynajem nieruchomości</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Materiały / surowce</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Przychody finansowe</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Usługi zewnętrzne</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Dotacje / dofinansowania</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Marketing i reklama</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Pozostałe przychody</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Pozostałe wydatki</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="10" t="inlineStr"/>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>✅  SUMA PRZYCHODÓW</t>
-        </is>
-      </c>
-      <c r="C10" s="12">
-        <f>SUM(C4:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>❌  SUMA WYDATKÓW</t>
-        </is>
-      </c>
-      <c r="F10" s="14">
-        <f>-SUM(F4:F9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="8" customHeight="1"/>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>💰  WYNIK NETTO (PRZYCHODY − WYDATKI)</t>
-        </is>
-      </c>
-      <c r="C12" s="16">
-        <f>C10+F10</f>
-        <v/>
-      </c>
-      <c r="D12" s="17">
-        <f> C10 (przychody)  +  F10 (wydatki ujemne)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>🔵 Komórki NIEBIESKIE = wpisz wartości  |  🟡 Żółte = pole do uzupełnienia  |  🟢 C10 = suma przychodów  |  🔴 F10 = suma wydatków (ujemna)</t>
-        </is>
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>📅  ZESTAWIENIE ROCZNE — PRZYCHODY / WYDATKI / WYNIK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Miesiąc</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>Styczeń</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>Luty</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>Marzec</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>Kwiecień</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>Maj</t>
+        </is>
+      </c>
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t>Czerwiec</t>
+        </is>
+      </c>
+      <c r="H2" s="23" t="inlineStr">
+        <is>
+          <t>Lipiec</t>
+        </is>
+      </c>
+      <c r="I2" s="23" t="inlineStr">
+        <is>
+          <t>Sierpień</t>
+        </is>
+      </c>
+      <c r="J2" s="23" t="inlineStr">
+        <is>
+          <t>Wrzesień</t>
+        </is>
+      </c>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>Październik</t>
+        </is>
+      </c>
+      <c r="L2" s="23" t="inlineStr">
+        <is>
+          <t>Listopad</t>
+        </is>
+      </c>
+      <c r="M2" s="23" t="inlineStr">
+        <is>
+          <t>Grudzień</t>
+        </is>
+      </c>
+      <c r="N2" s="38" t="inlineStr">
+        <is>
+          <t>RAZEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>Przychody (PLN)</t>
+        </is>
+      </c>
+      <c r="B3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="41">
+        <f>SUM(B3:M3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Wydatki (PLN)</t>
+        </is>
+      </c>
+      <c r="B4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="43">
+        <f>SUM(B4:M4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="44" t="inlineStr">
+        <is>
+          <t>Wynik netto (PLN)</t>
+        </is>
+      </c>
+      <c r="B5" s="45">
+        <f>B3-B4</f>
+        <v/>
+      </c>
+      <c r="C5" s="45">
+        <f>C3-C4</f>
+        <v/>
+      </c>
+      <c r="D5" s="45">
+        <f>D3-D4</f>
+        <v/>
+      </c>
+      <c r="E5" s="45">
+        <f>E3-E4</f>
+        <v/>
+      </c>
+      <c r="F5" s="45">
+        <f>F3-F4</f>
+        <v/>
+      </c>
+      <c r="G5" s="45">
+        <f>G3-G4</f>
+        <v/>
+      </c>
+      <c r="H5" s="45">
+        <f>H3-H4</f>
+        <v/>
+      </c>
+      <c r="I5" s="45">
+        <f>I3-I4</f>
+        <v/>
+      </c>
+      <c r="J5" s="45">
+        <f>J3-J4</f>
+        <v/>
+      </c>
+      <c r="K5" s="45">
+        <f>K3-K4</f>
+        <v/>
+      </c>
+      <c r="L5" s="45">
+        <f>L3-L4</f>
+        <v/>
+      </c>
+      <c r="M5" s="45">
+        <f>M3-M4</f>
+        <v/>
+      </c>
+      <c r="N5" s="46">
+        <f>N3-N4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>Marża (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="48">
+        <f>IF(B3=0,0,B5/B3)</f>
+        <v/>
+      </c>
+      <c r="C6" s="48">
+        <f>IF(C3=0,0,C5/C3)</f>
+        <v/>
+      </c>
+      <c r="D6" s="48">
+        <f>IF(D3=0,0,D5/D3)</f>
+        <v/>
+      </c>
+      <c r="E6" s="48">
+        <f>IF(E3=0,0,E5/E3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="48">
+        <f>IF(F3=0,0,F5/F3)</f>
+        <v/>
+      </c>
+      <c r="G6" s="48">
+        <f>IF(G3=0,0,G5/G3)</f>
+        <v/>
+      </c>
+      <c r="H6" s="48">
+        <f>IF(H3=0,0,H5/H3)</f>
+        <v/>
+      </c>
+      <c r="I6" s="48">
+        <f>IF(I3=0,0,I5/I3)</f>
+        <v/>
+      </c>
+      <c r="J6" s="48">
+        <f>IF(J3=0,0,J5/J3)</f>
+        <v/>
+      </c>
+      <c r="K6" s="48">
+        <f>IF(K3=0,0,K5/K3)</f>
+        <v/>
+      </c>
+      <c r="L6" s="48">
+        <f>IF(L3=0,0,L5/L3)</f>
+        <v/>
+      </c>
+      <c r="M6" s="48">
+        <f>IF(M3=0,0,M5/M3)</f>
+        <v/>
+      </c>
+      <c r="N6" s="49">
+        <f>IF(N3=0,0,N5/N3)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="A12:B12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>